--- a/data/performance/daily/signal_list_2026-05-13.xlsx
+++ b/data/performance/daily/signal_list_2026-05-13.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 28.0%  (26W / 67L of 93 evaluated)</t>
+          <t>Win Rate: 30.1%  (28W / 65L of 93 evaluated)</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1310</v>
+        <v>1340</v>
       </c>
       <c r="D7" t="n">
         <v>1270</v>
@@ -637,10 +637,10 @@
         <v>1315</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.38</v>
+        <v>-1.87</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-3.05</v>
+        <v>-5.22</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4380</v>
+        <v>4400</v>
       </c>
       <c r="D9" t="n">
         <v>4250</v>
@@ -721,10 +721,10 @@
         <v>4390</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.23</v>
+        <v>-0.23</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.97</v>
+        <v>-3.41</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>532.4</v>
+        <v>585</v>
       </c>
       <c r="D11" t="n">
         <v>523.38</v>
@@ -805,10 +805,10 @@
         <v>532.4</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0</v>
+        <v>-8.99</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.69</v>
+        <v>-10.53</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="D14" t="n">
         <v>1600</v>
@@ -931,10 +931,10 @@
         <v>1630</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.84</v>
+        <v>-2.14</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2370</v>
+        <v>2380</v>
       </c>
       <c r="D19" t="n">
         <v>2380</v>
@@ -1141,14 +1141,14 @@
         <v>2390</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.84</v>
+        <v>0.42</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17200</v>
+        <v>17225</v>
       </c>
       <c r="D20" t="n">
         <v>16675</v>
@@ -1183,10 +1183,10 @@
         <v>17200</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.05</v>
+        <v>-3.19</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="D21" t="n">
         <v>1200</v>
@@ -1225,10 +1225,10 @@
         <v>1240</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.4</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.83</v>
+        <v>-2.44</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D23" t="n">
         <v>147</v>
@@ -1309,10 +1309,10 @@
         <v>160</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.9</v>
+        <v>5.96</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-4.55</v>
+        <v>-2.65</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5700</v>
+        <v>5875</v>
       </c>
       <c r="D24" t="n">
         <v>5350</v>
@@ -1351,10 +1351,10 @@
         <v>5700</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0</v>
+        <v>-2.98</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-6.14</v>
+        <v>-8.94</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>755</v>
+        <v>785</v>
       </c>
       <c r="D25" t="n">
         <v>785</v>
@@ -1393,14 +1393,14 @@
         <v>785</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="D26" t="n">
         <v>635</v>
@@ -1435,10 +1435,10 @@
         <v>700</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>15.7</v>
+        <v>16.67</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.96</v>
+        <v>5.83</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="D27" t="n">
         <v>330</v>
@@ -1477,10 +1477,10 @@
         <v>346</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.76</v>
+        <v>4.85</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.94</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="D29" t="n">
         <v>404</v>
@@ -1561,10 +1561,10 @@
         <v>416</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.48</v>
+        <v>1.46</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.42</v>
+        <v>-1.46</v>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D31" t="n">
         <v>111</v>
@@ -1645,10 +1645,10 @@
         <v>117</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.86</v>
+        <v>1.74</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-4.31</v>
+        <v>-3.48</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="D32" t="n">
         <v>980</v>
@@ -1687,10 +1687,10 @@
         <v>1015</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0</v>
+        <v>-0.49</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-3.45</v>
+        <v>-3.92</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D33" t="n">
         <v>254</v>
@@ -1729,10 +1729,10 @@
         <v>262</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.77</v>
+        <v>-1.5</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-2.31</v>
+        <v>-4.51</v>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D34" t="n">
         <v>74</v>
@@ -1771,14 +1771,14 @@
         <v>74</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>0</v>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D35" t="n">
         <v>320</v>
@@ -1813,10 +1813,10 @@
         <v>334</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-3.03</v>
+        <v>-4.19</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2430</v>
+        <v>2420</v>
       </c>
       <c r="D36" t="n">
         <v>2400</v>
@@ -1855,10 +1855,10 @@
         <v>2440</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.41</v>
+        <v>0.83</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-1.23</v>
+        <v>-0.83</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>13000</v>
+        <v>13150</v>
       </c>
       <c r="D38" t="n">
         <v>12775</v>
@@ -1939,10 +1939,10 @@
         <v>13000</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-1.73</v>
+        <v>-2.85</v>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="D39" t="n">
         <v>535</v>
@@ -1981,10 +1981,10 @@
         <v>560</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-3.6</v>
+        <v>-4.46</v>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="D40" t="n">
         <v>420</v>
@@ -2023,10 +2023,10 @@
         <v>420</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2750</v>
+        <v>2550</v>
       </c>
       <c r="D42" t="n">
         <v>2670</v>
@@ -2107,14 +2107,14 @@
         <v>2890</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>5.09</v>
+        <v>13.33</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-2.91</v>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>4.71</v>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D43" t="n">
         <v>342</v>
@@ -2149,10 +2149,10 @@
         <v>354</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1.14</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>-2.29</v>
+        <v>-3.93</v>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D44" t="n">
         <v>122</v>
@@ -2191,10 +2191,10 @@
         <v>129</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.78</v>
+        <v>1.57</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-4.69</v>
+        <v>-3.94</v>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6850</v>
+        <v>6875</v>
       </c>
       <c r="D46" t="n">
         <v>6575</v>
@@ -2275,10 +2275,10 @@
         <v>6900</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.73</v>
+        <v>0.36</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-4.01</v>
+        <v>-4.36</v>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D48" t="n">
         <v>248</v>
@@ -2359,10 +2359,10 @@
         <v>268</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0</v>
+        <v>-1.47</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-7.46</v>
+        <v>-8.82</v>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D50" t="n">
         <v>127</v>
@@ -2443,10 +2443,10 @@
         <v>130</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>3.17</v>
+        <v>4</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>0.79</v>
+        <v>1.6</v>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D51" t="n">
         <v>92</v>
@@ -2485,10 +2485,10 @@
         <v>98</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>11.36</v>
+        <v>12.64</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>4.55</v>
+        <v>5.75</v>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D52" t="n">
         <v>316</v>
@@ -2527,10 +2527,10 @@
         <v>358</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>11.18</v>
+        <v>10.49</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-1.86</v>
+        <v>-2.47</v>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2860</v>
+        <v>2900</v>
       </c>
       <c r="D53" t="n">
         <v>2920</v>
@@ -2569,10 +2569,10 @@
         <v>2950</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>3.15</v>
+        <v>1.72</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>2.1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D56" t="n">
         <v>166</v>
@@ -2695,10 +2695,10 @@
         <v>174</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>7.41</v>
+        <v>5.45</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>2.47</v>
+        <v>0.61</v>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D57" t="n">
         <v>240</v>
@@ -2737,10 +2737,10 @@
         <v>240</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>13.21</v>
+        <v>2.56</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>13.21</v>
+        <v>2.56</v>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D58" t="n">
         <v>97</v>
@@ -2779,10 +2779,10 @@
         <v>104</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>0</v>
+        <v>-0.95</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-6.73</v>
+        <v>-7.62</v>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D59" t="n">
         <v>89</v>
@@ -2821,10 +2821,10 @@
         <v>95</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1.06</v>
+        <v>2.15</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>-5.32</v>
+        <v>-4.3</v>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D62" t="n">
         <v>224</v>
@@ -2947,10 +2947,10 @@
         <v>232</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>-2.61</v>
+        <v>-3.45</v>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4700</v>
+        <v>4710</v>
       </c>
       <c r="D64" t="n">
         <v>4600</v>
@@ -3031,10 +3031,10 @@
         <v>4720</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>0.43</v>
+        <v>0.21</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-2.13</v>
+        <v>-2.34</v>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D66" t="n">
         <v>100</v>
@@ -3115,10 +3115,10 @@
         <v>106</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>10.42</v>
+        <v>11.58</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>4.17</v>
+        <v>5.26</v>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D68" t="n">
         <v>71</v>
@@ -3199,10 +3199,10 @@
         <v>76</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>-6.58</v>
+        <v>-7.79</v>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D69" t="n">
         <v>52</v>
@@ -3241,14 +3241,14 @@
         <v>52</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>8.33</v>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="D71" t="n">
         <v>965</v>
@@ -3325,10 +3325,10 @@
         <v>985</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>-1.03</v>
+        <v>-0.52</v>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D72" t="n">
         <v>82</v>
@@ -3367,10 +3367,10 @@
         <v>88</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>8.640000000000001</v>
+        <v>10</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>1.23</v>
+        <v>2.5</v>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D76" t="n">
         <v>117</v>
@@ -3535,14 +3535,14 @@
         <v>126</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>2.44</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-4.88</v>
-      </c>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.86</v>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D78" t="n">
         <v>80</v>
@@ -3619,14 +3619,14 @@
         <v>86</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>6.17</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>1.27</v>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D79" t="n">
         <v>66</v>
@@ -3661,10 +3661,10 @@
         <v>66</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>0</v>
+        <v>-1.49</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>0</v>
+        <v>-1.49</v>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D80" t="n">
         <v>157</v>
@@ -3703,10 +3703,10 @@
         <v>165</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>2.48</v>
+        <v>3.12</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>-2.48</v>
+        <v>-1.88</v>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>630</v>
+        <v>615</v>
       </c>
       <c r="D81" t="n">
         <v>640</v>
@@ -3745,10 +3745,10 @@
         <v>645</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2.38</v>
+        <v>4.88</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>1.59</v>
+        <v>4.07</v>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>358</v>
+        <v>328</v>
       </c>
       <c r="D85" t="n">
         <v>346</v>
@@ -3913,14 +3913,14 @@
         <v>410</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>14.53</v>
+        <v>25</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>-3.35</v>
-      </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>5.49</v>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="D86" t="n">
         <v>402</v>
@@ -3955,10 +3955,10 @@
         <v>406</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>5.18</v>
+        <v>9.73</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>4.15</v>
+        <v>8.65</v>
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D88" t="n">
         <v>111</v>
@@ -4039,10 +4039,10 @@
         <v>114</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>0</v>
+        <v>-0.87</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>-2.63</v>
+        <v>-3.48</v>
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>990</v>
+        <v>980</v>
       </c>
       <c r="D89" t="n">
         <v>985</v>
@@ -4081,14 +4081,14 @@
         <v>1015</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>2.53</v>
+        <v>3.57</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="H89" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.51</v>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D91" t="n">
         <v>80</v>
@@ -4165,10 +4165,10 @@
         <v>87</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>17.57</v>
+        <v>16</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>8.109999999999999</v>
+        <v>6.67</v>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="D95" t="n">
         <v>595</v>
@@ -4333,14 +4333,14 @@
         <v>595</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>0.85</v>
+        <v>-0.83</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H95" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-0.83</v>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2500</v>
+        <v>2520</v>
       </c>
       <c r="D97" t="n">
         <v>2460</v>
@@ -4417,10 +4417,10 @@
         <v>2510</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>0.4</v>
+        <v>-0.4</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>-1.6</v>
+        <v>-2.38</v>
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">

--- a/data/performance/daily/signal_list_2026-05-13.xlsx
+++ b/data/performance/daily/signal_list_2026-05-13.xlsx
@@ -55,12 +55,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -469,14 +469,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Swing Signal List — 2026-05-13</t>
+          <t>Swing — Review sesi market 2026-05-13</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 30.1%  (28W / 65L of 93 evaluated)</t>
+          <t>Win Rate: 38.0%  (38W / 62L of 100 evaluated)</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AKRA.JK</t>
+          <t>AALI.JK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -544,28 +544,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1455</v>
+        <v>8075</v>
       </c>
       <c r="D5" t="n">
-        <v>1465</v>
+        <v>7600</v>
       </c>
       <c r="E5" t="n">
-        <v>1485</v>
+        <v>7800</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2.06</v>
+        <v>-3.41</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>-5.88</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AUTO.JK</t>
+          <t>BCIP.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -586,28 +586,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2590</v>
+        <v>76</v>
       </c>
       <c r="D6" t="n">
-        <v>2630</v>
+        <v>74</v>
       </c>
       <c r="E6" t="n">
-        <v>2670</v>
+        <v>79</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.09</v>
+        <v>3.95</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.54</v>
+        <v>-2.63</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BBTN.JK</t>
+          <t>BDMN.JK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -628,28 +628,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1340</v>
+        <v>4390</v>
       </c>
       <c r="D7" t="n">
-        <v>1270</v>
+        <v>4400</v>
       </c>
       <c r="E7" t="n">
-        <v>1315</v>
+        <v>4570</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.87</v>
+        <v>4.1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-5.22</v>
+        <v>0.23</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIP.JK</t>
+          <t>BJBR.JK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -670,28 +670,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>74</v>
+        <v>795</v>
       </c>
       <c r="D8" t="n">
-        <v>72</v>
+        <v>785</v>
       </c>
       <c r="E8" t="n">
-        <v>75</v>
+        <v>795</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
+        <v>-1.26</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BDMN.JK</t>
+          <t>BJTM.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -712,28 +712,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4400</v>
+        <v>590</v>
       </c>
       <c r="D9" t="n">
-        <v>4250</v>
+        <v>585</v>
       </c>
       <c r="E9" t="n">
-        <v>4390</v>
+        <v>590</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-3.41</v>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
+        <v>-0.85</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BJBR.JK</t>
+          <t>BNLI.JK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -754,28 +754,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>785</v>
+        <v>3290</v>
       </c>
       <c r="D10" t="n">
-        <v>780</v>
+        <v>3340</v>
       </c>
       <c r="E10" t="n">
-        <v>790</v>
+        <v>3370</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.64</v>
+        <v>2.43</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.64</v>
+        <v>1.52</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BJTM.JK</t>
+          <t>BRAM.JK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -796,28 +796,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>585</v>
+        <v>4560</v>
       </c>
       <c r="D11" t="n">
-        <v>523.38</v>
+        <v>4470</v>
       </c>
       <c r="E11" t="n">
-        <v>532.4</v>
+        <v>4510</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-8.99</v>
+        <v>-1.1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-10.53</v>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
+        <v>-1.97</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -829,7 +829,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEKA.JK</t>
+          <t>CFIN.JK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -838,28 +838,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2390</v>
+        <v>350</v>
       </c>
       <c r="D12" t="n">
-        <v>2360</v>
+        <v>348</v>
       </c>
       <c r="E12" t="n">
-        <v>2410</v>
+        <v>352</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.84</v>
+        <v>0.57</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
+        <v>-0.57</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CFIN.JK</t>
+          <t>CLPI.JK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -880,28 +880,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>348</v>
+        <v>1620</v>
       </c>
       <c r="D13" t="n">
-        <v>342</v>
+        <v>1635</v>
       </c>
       <c r="E13" t="n">
-        <v>348</v>
+        <v>1635</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.72</v>
+        <v>0.93</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -913,7 +913,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CLPI.JK</t>
+          <t>DMAS.JK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -922,28 +922,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1635</v>
+        <v>152</v>
       </c>
       <c r="D14" t="n">
-        <v>1600</v>
+        <v>152</v>
       </c>
       <c r="E14" t="n">
-        <v>1630</v>
+        <v>153</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.31</v>
+        <v>0.66</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.14</v>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -955,7 +955,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>DUTI.JK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -964,28 +964,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>179</v>
+        <v>4100</v>
       </c>
       <c r="D15" t="n">
-        <v>167</v>
+        <v>4200</v>
       </c>
       <c r="E15" t="n">
-        <v>180</v>
+        <v>4200</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.44</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-6.7</v>
+        <v>2.44</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -997,7 +997,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DLTA.JK</t>
+          <t>EPMT.JK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1006,28 +1006,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2000</v>
+        <v>2390</v>
       </c>
       <c r="D16" t="n">
-        <v>1970</v>
+        <v>2380</v>
       </c>
       <c r="E16" t="n">
-        <v>2000</v>
+        <v>2400</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
+        <v>-0.42</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DMAS.JK</t>
+          <t>GGRM.JK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>152</v>
+        <v>16625</v>
       </c>
       <c r="D17" t="n">
-        <v>154</v>
+        <v>17225</v>
       </c>
       <c r="E17" t="n">
-        <v>156</v>
+        <v>17450</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.63</v>
+        <v>4.96</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
+        <v>3.61</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1081,37 +1081,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>GJTL.JK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PRE_MARKUP</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>76</v>
+        <v>1205</v>
       </c>
       <c r="D18" t="n">
-        <v>73</v>
+        <v>1230</v>
       </c>
       <c r="E18" t="n">
-        <v>77</v>
+        <v>1265</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.32</v>
+        <v>4.98</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.95</v>
+        <v>2.07</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1123,7 +1123,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EPMT.JK</t>
+          <t>GSMF.JK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1132,28 +1132,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2380</v>
+        <v>131</v>
       </c>
       <c r="D19" t="n">
-        <v>2380</v>
+        <v>138</v>
       </c>
       <c r="E19" t="n">
-        <v>2390</v>
+        <v>140</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.42</v>
+        <v>6.87</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1165,7 +1165,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GGRM.JK</t>
+          <t>HEXA.JK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1174,28 +1174,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17225</v>
+        <v>4500</v>
       </c>
       <c r="D20" t="n">
-        <v>16675</v>
+        <v>4490</v>
       </c>
       <c r="E20" t="n">
-        <v>17200</v>
+        <v>4500</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.19</v>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
+        <v>-0.22</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1207,7 +1207,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GJTL.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1216,28 +1216,28 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1230</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>1200</v>
+        <v>151</v>
       </c>
       <c r="E21" t="n">
-        <v>1240</v>
+        <v>153</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>16.79</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.44</v>
+        <v>15.27</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1249,37 +1249,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GSMF.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PRE_MARKUP</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>138</v>
+        <v>6075</v>
       </c>
       <c r="D22" t="n">
-        <v>155</v>
+        <v>5875</v>
       </c>
       <c r="E22" t="n">
-        <v>158</v>
+        <v>6050</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>14.49</v>
+        <v>-0.41</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>12.32</v>
+        <v>-3.29</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1291,7 +1291,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>IPOL.JK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1300,28 +1300,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="D23" t="n">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="E23" t="n">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5.96</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.65</v>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
+        <v>-1.63</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>KBLM.JK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1342,28 +1342,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5875</v>
+        <v>336</v>
       </c>
       <c r="D24" t="n">
-        <v>5350</v>
+        <v>330</v>
       </c>
       <c r="E24" t="n">
-        <v>5700</v>
+        <v>336</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.98</v>
+        <v>0</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-8.94</v>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
+        <v>-1.79</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1375,7 +1375,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>INPP.JK</t>
+          <t>LPIN.JK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1384,28 +1384,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>785</v>
+        <v>430</v>
       </c>
       <c r="D25" t="n">
-        <v>785</v>
+        <v>410</v>
       </c>
       <c r="E25" t="n">
-        <v>785</v>
+        <v>430</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
+        <v>-4.65</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KAEF.JK</t>
+          <t>MAPI.JK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1426,28 +1426,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>600</v>
+        <v>1495</v>
       </c>
       <c r="D26" t="n">
-        <v>635</v>
+        <v>1475</v>
       </c>
       <c r="E26" t="n">
-        <v>700</v>
+        <v>1500</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>16.67</v>
+        <v>0.33</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.83</v>
+        <v>-1.34</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1459,7 +1459,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KBLM.JK</t>
+          <t>MICE.JK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1468,28 +1468,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="D27" t="n">
-        <v>330</v>
+        <v>510</v>
       </c>
       <c r="E27" t="n">
-        <v>346</v>
+        <v>515</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4.85</v>
+        <v>3</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1501,7 +1501,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>MIDI.JK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,28 +1510,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3390</v>
+        <v>336</v>
       </c>
       <c r="D28" t="n">
-        <v>2890</v>
+        <v>320</v>
       </c>
       <c r="E28" t="n">
-        <v>3390</v>
+        <v>322</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0</v>
+        <v>-4.17</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-14.75</v>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
+        <v>-4.76</v>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1543,7 +1543,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LPIN.JK</t>
+          <t>MLBI.JK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1552,28 +1552,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>410</v>
+        <v>6275</v>
       </c>
       <c r="D29" t="n">
-        <v>404</v>
+        <v>6125</v>
       </c>
       <c r="E29" t="n">
-        <v>416</v>
+        <v>6300</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.46</v>
+        <v>0.4</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.46</v>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
+        <v>-2.39</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MAPI.JK</t>
+          <t>NIKL.JK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1594,28 +1594,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1475</v>
+        <v>330</v>
       </c>
       <c r="D30" t="n">
-        <v>1485</v>
+        <v>326</v>
       </c>
       <c r="E30" t="n">
-        <v>1495</v>
+        <v>344</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.36</v>
+        <v>4.24</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.68</v>
+        <v>-1.21</v>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1636,28 +1636,28 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>114</v>
+      </c>
+      <c r="D31" t="n">
         <v>115</v>
       </c>
-      <c r="D31" t="n">
-        <v>111</v>
-      </c>
       <c r="E31" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.74</v>
+        <v>4.39</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.48</v>
+        <v>0.88</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1669,7 +1669,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PNBN.JK</t>
+          <t>PANS.JK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1678,28 +1678,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1020</v>
+        <v>1730</v>
       </c>
       <c r="D32" t="n">
-        <v>980</v>
+        <v>1735</v>
       </c>
       <c r="E32" t="n">
-        <v>1015</v>
+        <v>1745</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.49</v>
+        <v>0.87</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-3.92</v>
+        <v>0.29</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PNLF.JK</t>
+          <t>PNBN.JK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1720,28 +1720,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>266</v>
+        <v>1020</v>
       </c>
       <c r="D33" t="n">
-        <v>254</v>
+        <v>1020</v>
       </c>
       <c r="E33" t="n">
-        <v>262</v>
+        <v>1030</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.5</v>
+        <v>0.98</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-4.51</v>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1753,7 +1753,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>PNLF.JK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1762,28 +1762,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>74</v>
+        <v>266</v>
       </c>
       <c r="D34" t="n">
-        <v>74</v>
+        <v>266</v>
       </c>
       <c r="E34" t="n">
-        <v>74</v>
+        <v>270</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SAME.JK</t>
+          <t>PYFA.JK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1804,28 +1804,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="D35" t="n">
         <v>320</v>
       </c>
       <c r="E35" t="n">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-4.19</v>
-      </c>
-      <c r="H35" s="6" t="inlineStr">
+        <v>-1.23</v>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SCCO.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1846,28 +1846,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2420</v>
+        <v>70</v>
       </c>
       <c r="D36" t="n">
-        <v>2400</v>
+        <v>74</v>
       </c>
       <c r="E36" t="n">
-        <v>2440</v>
+        <v>74</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.83</v>
+        <v>5.71</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-0.83</v>
+        <v>5.71</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1879,7 +1879,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SMSM.JK</t>
+          <t>SAME.JK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1888,28 +1888,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1860</v>
+        <v>334</v>
       </c>
       <c r="D37" t="n">
-        <v>1865</v>
+        <v>334</v>
       </c>
       <c r="E37" t="n">
-        <v>1865</v>
+        <v>334</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -1921,7 +1921,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>UNIC.JK</t>
+          <t>SCCO.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1930,28 +1930,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>13150</v>
+        <v>2460</v>
       </c>
       <c r="D38" t="n">
-        <v>12775</v>
+        <v>2420</v>
       </c>
       <c r="E38" t="n">
-        <v>13000</v>
+        <v>2460</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-2.85</v>
-      </c>
-      <c r="H38" s="6" t="inlineStr">
+        <v>-1.63</v>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -1963,7 +1963,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WINS.JK</t>
+          <t>SMSM.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1972,28 +1972,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>560</v>
+        <v>1860</v>
       </c>
       <c r="D39" t="n">
-        <v>535</v>
+        <v>1860</v>
       </c>
       <c r="E39" t="n">
-        <v>560</v>
+        <v>1865</v>
       </c>
       <c r="F39" s="4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="4" t="n">
-        <v>-4.46</v>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2005,7 +2005,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>406</v>
+        <v>695</v>
       </c>
       <c r="D40" t="n">
-        <v>420</v>
+        <v>715</v>
       </c>
       <c r="E40" t="n">
-        <v>420</v>
+        <v>760</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>3.45</v>
+        <v>9.35</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
+        <v>2.88</v>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2047,7 +2047,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>POWR.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2056,28 +2056,28 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>770</v>
+        <v>3640</v>
       </c>
       <c r="D41" t="n">
-        <v>775</v>
+        <v>3670</v>
       </c>
       <c r="E41" t="n">
-        <v>790</v>
+        <v>3700</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2.6</v>
+        <v>1.65</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
+        <v>0.82</v>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>TOTL.JK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2098,28 +2098,28 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2550</v>
+        <v>1235</v>
       </c>
       <c r="D42" t="n">
-        <v>2670</v>
+        <v>1230</v>
       </c>
       <c r="E42" t="n">
-        <v>2890</v>
+        <v>1240</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>13.33</v>
+        <v>0.4</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>4.71</v>
+        <v>-0.4</v>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2131,7 +2131,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>TRST.JK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2140,28 +2140,28 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>356</v>
+        <v>480</v>
       </c>
       <c r="D43" t="n">
-        <v>342</v>
+        <v>472</v>
       </c>
       <c r="E43" t="n">
-        <v>354</v>
+        <v>478</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.42</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>-3.93</v>
-      </c>
-      <c r="H43" s="6" t="inlineStr">
+        <v>-1.67</v>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2173,7 +2173,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>ULTJ.JK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2182,28 +2182,28 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>127</v>
+        <v>1615</v>
       </c>
       <c r="D44" t="n">
-        <v>122</v>
+        <v>1605</v>
       </c>
       <c r="E44" t="n">
-        <v>129</v>
+        <v>1620</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1.57</v>
+        <v>0.31</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-3.94</v>
-      </c>
-      <c r="H44" s="6" t="inlineStr">
+        <v>-0.62</v>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2215,7 +2215,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>UNIC.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2224,28 +2224,28 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>865</v>
+        <v>12900</v>
       </c>
       <c r="D45" t="n">
-        <v>850</v>
+        <v>13150</v>
       </c>
       <c r="E45" t="n">
-        <v>865</v>
+        <v>13500</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>-1.73</v>
+        <v>1.94</v>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2257,7 +2257,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>WINS.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2266,28 +2266,28 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6875</v>
+        <v>565</v>
       </c>
       <c r="D46" t="n">
-        <v>6575</v>
+        <v>560</v>
       </c>
       <c r="E46" t="n">
-        <v>6900</v>
+        <v>565</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-4.36</v>
-      </c>
-      <c r="H46" s="6" t="inlineStr">
+        <v>-0.88</v>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2299,7 +2299,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PBID.JK</t>
+          <t>JGLE.JK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2308,28 +2308,28 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>555</v>
+        <v>76</v>
       </c>
       <c r="D47" t="n">
-        <v>550</v>
+        <v>82</v>
       </c>
       <c r="E47" t="n">
-        <v>555</v>
+        <v>83</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>-0.9</v>
+        <v>7.89</v>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>JMAS.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2350,28 +2350,28 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>272</v>
+        <v>378</v>
       </c>
       <c r="D48" t="n">
-        <v>248</v>
+        <v>406</v>
       </c>
       <c r="E48" t="n">
-        <v>268</v>
+        <v>416</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>-1.47</v>
+        <v>10.05</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-8.82</v>
+        <v>7.41</v>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GHON.JK</t>
+          <t>POWR.JK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2392,28 +2392,28 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1815</v>
+        <v>765</v>
       </c>
       <c r="D49" t="n">
-        <v>1800</v>
+        <v>770</v>
       </c>
       <c r="E49" t="n">
-        <v>1815</v>
+        <v>775</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>-0.83</v>
+        <v>0.65</v>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DFAM.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2434,28 +2434,28 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>125</v>
+        <v>2570</v>
       </c>
       <c r="D50" t="n">
-        <v>127</v>
+        <v>2550</v>
       </c>
       <c r="E50" t="n">
-        <v>130</v>
+        <v>2570</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>1.6</v>
+        <v>-0.78</v>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2467,7 +2467,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2476,28 +2476,28 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>87</v>
+        <v>346</v>
       </c>
       <c r="D51" t="n">
-        <v>92</v>
+        <v>356</v>
       </c>
       <c r="E51" t="n">
-        <v>98</v>
+        <v>374</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>12.64</v>
+        <v>8.09</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
+        <v>2.89</v>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2509,7 +2509,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2518,28 +2518,28 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>324</v>
+        <v>875</v>
       </c>
       <c r="D52" t="n">
-        <v>316</v>
+        <v>865</v>
       </c>
       <c r="E52" t="n">
-        <v>358</v>
+        <v>890</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>10.49</v>
+        <v>1.71</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-2.47</v>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
+        <v>-1.14</v>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2551,7 +2551,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CLAY.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2560,28 +2560,28 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2900</v>
+        <v>7650</v>
       </c>
       <c r="D53" t="n">
-        <v>2920</v>
+        <v>6875</v>
       </c>
       <c r="E53" t="n">
-        <v>2950</v>
+        <v>7350</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1.72</v>
+        <v>-3.92</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>-10.13</v>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CCSI.JK</t>
+          <t>PBID.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2602,28 +2602,28 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>278</v>
+        <v>550</v>
       </c>
       <c r="D54" t="n">
-        <v>260</v>
+        <v>555</v>
       </c>
       <c r="E54" t="n">
-        <v>284</v>
+        <v>555</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2.16</v>
+        <v>0.91</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-6.47</v>
+        <v>0.91</v>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -2635,7 +2635,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>INPS.JK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2644,28 +2644,28 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>168</v>
+        <v>610</v>
       </c>
       <c r="D55" t="n">
-        <v>157</v>
+        <v>610</v>
       </c>
       <c r="E55" t="n">
-        <v>170</v>
+        <v>610</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>-6.55</v>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -2677,7 +2677,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>DFAM.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2686,28 +2686,28 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="D56" t="n">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="E56" t="n">
-        <v>174</v>
+        <v>130</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>5.45</v>
+        <v>4.84</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -2719,7 +2719,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2728,28 +2728,28 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D57" t="n">
-        <v>240</v>
+        <v>87</v>
       </c>
       <c r="E57" t="n">
-        <v>240</v>
+        <v>93</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2.56</v>
+        <v>3.33</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>2.56</v>
+        <v>-3.33</v>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2761,7 +2761,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>MOLI.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2770,28 +2770,28 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="D58" t="n">
-        <v>97</v>
+        <v>274</v>
       </c>
       <c r="E58" t="n">
-        <v>104</v>
+        <v>284</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>-0.95</v>
+        <v>5.19</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-7.62</v>
+        <v>1.48</v>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2803,7 +2803,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>PANI.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2812,28 +2812,28 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>93</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="n">
-        <v>89</v>
+        <v>8350</v>
       </c>
       <c r="E59" t="n">
-        <v>95</v>
+        <v>8550</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2.15</v>
+        <v>1.18</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="H59" s="6" t="inlineStr">
+        <v>-1.18</v>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2845,7 +2845,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NPGF.JK</t>
+          <t>PAMG.JK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2854,28 +2854,28 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D60" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2.7</v>
+        <v>3.33</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-5.41</v>
-      </c>
-      <c r="H60" s="6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -2887,7 +2887,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LABA.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2896,28 +2896,28 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="D61" t="n">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="E61" t="n">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>-7.44</v>
-      </c>
-      <c r="H61" s="6" t="inlineStr">
+        <v>-2.16</v>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2929,7 +2929,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>UVCR.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2938,28 +2938,28 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>232</v>
+        <v>178</v>
       </c>
       <c r="D62" t="n">
-        <v>224</v>
+        <v>165</v>
       </c>
       <c r="E62" t="n">
-        <v>232</v>
+        <v>184</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>-3.45</v>
-      </c>
-      <c r="H62" s="6" t="inlineStr">
+        <v>-7.3</v>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -2971,7 +2971,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>RSGK.JK</t>
+          <t>PGJO.JK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1190</v>
+        <v>800</v>
       </c>
       <c r="D63" t="n">
-        <v>1085</v>
+        <v>880</v>
       </c>
       <c r="E63" t="n">
-        <v>1190</v>
+        <v>880</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>-8.82</v>
+        <v>10</v>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3013,37 +3013,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CMRY.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PRE_MARKUP</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4710</v>
+        <v>214</v>
       </c>
       <c r="D64" t="n">
-        <v>4600</v>
+        <v>234</v>
       </c>
       <c r="E64" t="n">
-        <v>4720</v>
+        <v>234</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>0.21</v>
+        <v>9.35</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-2.34</v>
+        <v>9.35</v>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3055,7 +3055,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BSML.JK</t>
+          <t>KBAG.JK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3064,28 +3064,28 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>418</v>
+        <v>48</v>
       </c>
       <c r="D65" t="n">
-        <v>420</v>
+        <v>48</v>
       </c>
       <c r="E65" t="n">
-        <v>420</v>
+        <v>49</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>0.48</v>
+        <v>2.08</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3097,7 +3097,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3106,28 +3106,28 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="D66" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E66" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>11.58</v>
+        <v>-0.91</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>5.26</v>
+        <v>-4.55</v>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3139,7 +3139,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ASHA.JK</t>
+          <t>CASH.JK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3148,28 +3148,28 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>74</v>
+        <v>232</v>
       </c>
       <c r="D67" t="n">
-        <v>71</v>
+        <v>244</v>
       </c>
       <c r="E67" t="n">
-        <v>75</v>
+        <v>244</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1.35</v>
+        <v>5.17</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-4.05</v>
+        <v>5.17</v>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3181,7 +3181,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3190,28 +3190,28 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D68" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E68" t="n">
         <v>76</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>-7.79</v>
-      </c>
-      <c r="H68" s="6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3223,7 +3223,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>KKES.JK</t>
+          <t>BBSI.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3232,28 +3232,28 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>48</v>
+        <v>4740</v>
       </c>
       <c r="D69" t="n">
-        <v>52</v>
+        <v>4700</v>
       </c>
       <c r="E69" t="n">
-        <v>52</v>
+        <v>4740</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>8.33</v>
+        <v>-0.84</v>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3265,7 +3265,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3274,28 +3274,28 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="D70" t="n">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="E70" t="n">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>22.64</v>
+        <v>7.87</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>10.38</v>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
+        <v>4.49</v>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3307,7 +3307,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>VICI.JK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3316,28 +3316,28 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>970</v>
+        <v>580</v>
       </c>
       <c r="D71" t="n">
-        <v>965</v>
+        <v>580</v>
       </c>
       <c r="E71" t="n">
-        <v>985</v>
+        <v>600</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="H71" s="6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3349,7 +3349,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>HALO.JK</t>
+          <t>NPGF.JK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3358,28 +3358,28 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D72" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E72" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>10</v>
+        <v>2.63</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>2.5</v>
+        <v>-2.63</v>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3391,7 +3391,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PTMP.JK</t>
+          <t>UVCR.JK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3400,28 +3400,28 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>72</v>
+        <v>226</v>
       </c>
       <c r="D73" t="n">
-        <v>70</v>
+        <v>232</v>
       </c>
       <c r="E73" t="n">
-        <v>72</v>
+        <v>234</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>-2.78</v>
+        <v>2.65</v>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3433,7 +3433,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MPXL.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3442,28 +3442,28 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>193</v>
+        <v>276</v>
       </c>
       <c r="D74" t="n">
-        <v>172</v>
+        <v>272</v>
       </c>
       <c r="E74" t="n">
-        <v>197</v>
+        <v>282</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>-10.88</v>
-      </c>
-      <c r="H74" s="6" t="inlineStr">
+        <v>-1.45</v>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3475,7 +3475,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>KLAS.JK</t>
+          <t>CMRY.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3484,28 +3484,28 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>81</v>
+        <v>4740</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>4710</v>
       </c>
       <c r="E75" t="n">
-        <v>82</v>
+        <v>4770</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1.23</v>
+        <v>0.63</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="H75" s="6" t="inlineStr">
+        <v>-0.63</v>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3517,7 +3517,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>WMPP.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3526,28 +3526,28 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="D76" t="n">
-        <v>117</v>
+        <v>41</v>
       </c>
       <c r="E76" t="n">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>8.619999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3559,7 +3559,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3568,28 +3568,28 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D77" t="n">
         <v>95</v>
       </c>
       <c r="E77" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1.02</v>
+        <v>6.19</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>-3.06</v>
-      </c>
-      <c r="H77" s="6" t="inlineStr">
+        <v>-2.06</v>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SURI.JK</t>
+          <t>ASHA.JK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3610,28 +3610,28 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D78" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E78" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>8.859999999999999</v>
+        <v>5.41</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3643,7 +3643,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GRPH.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3652,28 +3652,28 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="D79" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E79" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>-1.49</v>
+        <v>11.11</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H79" s="6" t="inlineStr">
+        <v>-4.94</v>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3685,37 +3685,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HYGN.JK</t>
+          <t>KKES.JK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PRE_MARKUP</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>160</v>
+        <v>44</v>
       </c>
       <c r="D80" t="n">
-        <v>157</v>
+        <v>48</v>
       </c>
       <c r="E80" t="n">
-        <v>165</v>
+        <v>48</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>3.12</v>
+        <v>9.09</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>-1.88</v>
+        <v>9.09</v>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3727,7 +3727,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>TOOL.JK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3736,28 +3736,28 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>615</v>
+        <v>80</v>
       </c>
       <c r="D81" t="n">
-        <v>640</v>
+        <v>76</v>
       </c>
       <c r="E81" t="n">
-        <v>645</v>
+        <v>80</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>4.07</v>
+        <v>-5</v>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3769,7 +3769,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>VTNY.JK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3778,28 +3778,28 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="D82" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="E82" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1.05</v>
+        <v>2.86</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>-4.21</v>
-      </c>
-      <c r="H82" s="6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3811,7 +3811,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3820,28 +3820,28 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>176</v>
+        <v>910</v>
       </c>
       <c r="D83" t="n">
-        <v>192</v>
+        <v>970</v>
       </c>
       <c r="E83" t="n">
-        <v>216</v>
+        <v>980</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>22.73</v>
+        <v>7.69</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="H83" s="5" t="inlineStr">
+        <v>6.59</v>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3853,7 +3853,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>HALO.JK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3862,28 +3862,28 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>590</v>
+        <v>84</v>
       </c>
       <c r="D84" t="n">
-        <v>535</v>
+        <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>590</v>
+        <v>85</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>-9.32</v>
-      </c>
-      <c r="H84" s="6" t="inlineStr">
+        <v>-4.76</v>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>KSIX.JK</t>
+          <t>MPXL.JK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3904,28 +3904,28 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>328</v>
+        <v>191</v>
       </c>
       <c r="D85" t="n">
-        <v>346</v>
+        <v>193</v>
       </c>
       <c r="E85" t="n">
-        <v>410</v>
+        <v>198</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>25</v>
+        <v>3.66</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="H85" s="5" t="inlineStr">
+        <v>1.05</v>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3937,7 +3937,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>KLAS.JK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>370</v>
+        <v>84</v>
       </c>
       <c r="D86" t="n">
-        <v>402</v>
+        <v>81</v>
       </c>
       <c r="E86" t="n">
-        <v>406</v>
+        <v>84</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>9.73</v>
+        <v>0</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>8.65</v>
+        <v>-3.57</v>
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3979,7 +3979,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3988,28 +3988,28 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="D87" t="n">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="E87" t="n">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>9.77</v>
+        <v>2.02</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="6" t="inlineStr">
+        <v>-1.01</v>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4021,7 +4021,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>KAQI.JK</t>
+          <t>SURI.JK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4030,28 +4030,28 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="D88" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E88" t="n">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>-0.87</v>
+        <v>0</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>-3.48</v>
-      </c>
-      <c r="H88" s="6" t="inlineStr">
+        <v>-4.82</v>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4063,7 +4063,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FORE.JK</t>
+          <t>GRPH.JK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4072,28 +4072,28 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>980</v>
+        <v>67</v>
       </c>
       <c r="D89" t="n">
-        <v>985</v>
+        <v>67</v>
       </c>
       <c r="E89" t="n">
-        <v>1015</v>
+        <v>68</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>3.57</v>
+        <v>1.49</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4105,7 +4105,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MDLA.JK</t>
+          <t>HYGN.JK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4114,28 +4114,28 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>220</v>
+        <v>155</v>
       </c>
       <c r="D90" t="n">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="E90" t="n">
-        <v>222</v>
+        <v>166</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>0.91</v>
+        <v>7.1</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -4147,7 +4147,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4156,28 +4156,28 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="D91" t="n">
-        <v>80</v>
+        <v>590</v>
       </c>
       <c r="E91" t="n">
-        <v>87</v>
+        <v>605</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="H91" s="5" t="inlineStr">
+        <v>18</v>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -4189,7 +4189,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4198,28 +4198,28 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>520</v>
+        <v>330</v>
       </c>
       <c r="D92" t="n">
-        <v>494</v>
+        <v>370</v>
       </c>
       <c r="E92" t="n">
-        <v>520</v>
+        <v>372</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>0</v>
+        <v>12.73</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>-5</v>
+        <v>12.12</v>
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -4231,7 +4231,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ESTA.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4240,28 +4240,28 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>208</v>
+        <v>134</v>
       </c>
       <c r="D93" t="n">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="E93" t="n">
-        <v>216</v>
+        <v>137</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>3.85</v>
+        <v>2.24</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="H93" s="6" t="inlineStr">
+        <v>-0.75</v>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4273,7 +4273,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>KAQI.JK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4282,28 +4282,28 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="D94" t="n">
-        <v>179</v>
+        <v>115</v>
       </c>
       <c r="E94" t="n">
-        <v>181</v>
+        <v>127</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>5.83</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="H94" s="6" t="inlineStr">
+        <v>-4.17</v>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -4315,7 +4315,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>FORE.JK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4324,28 +4324,28 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>600</v>
+        <v>985</v>
       </c>
       <c r="D95" t="n">
-        <v>595</v>
+        <v>980</v>
       </c>
       <c r="E95" t="n">
-        <v>595</v>
+        <v>1035</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>-0.83</v>
+        <v>5.08</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="H95" s="6" t="inlineStr">
+        <v>-0.51</v>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -4357,7 +4357,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ADMF.JK</t>
+          <t>MDLA.JK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4366,28 +4366,28 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>8575</v>
+        <v>224</v>
       </c>
       <c r="D96" t="n">
-        <v>8500</v>
+        <v>220</v>
       </c>
       <c r="E96" t="n">
-        <v>8625</v>
+        <v>226</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>0.58</v>
+        <v>0.89</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="H96" s="6" t="inlineStr">
+        <v>-1.79</v>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -4399,40 +4399,334 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>DKHH.JK</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>78</v>
+      </c>
+      <c r="D97" t="n">
+        <v>75</v>
+      </c>
+      <c r="E97" t="n">
+        <v>79</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ASPI.JK</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>515</v>
+      </c>
+      <c r="D98" t="n">
+        <v>520</v>
+      </c>
+      <c r="E98" t="n">
+        <v>520</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>CGAS.JK</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>179</v>
+      </c>
+      <c r="D99" t="n">
+        <v>180</v>
+      </c>
+      <c r="E99" t="n">
+        <v>185</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>MSJA.JK</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>452</v>
+      </c>
+      <c r="D100" t="n">
+        <v>418</v>
+      </c>
+      <c r="E100" t="n">
+        <v>456</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>-7.52</v>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MANG.JK</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>51</v>
+      </c>
+      <c r="D101" t="n">
+        <v>52</v>
+      </c>
+      <c r="E101" t="n">
+        <v>53</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>KETR.JK</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>585</v>
+      </c>
+      <c r="D102" t="n">
+        <v>600</v>
+      </c>
+      <c r="E102" t="n">
+        <v>630</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ADMF.JK</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>8725</v>
+      </c>
+      <c r="D103" t="n">
+        <v>8575</v>
+      </c>
+      <c r="E103" t="n">
+        <v>8750</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>ADRO.JK</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>BREAKOUT</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>2600</v>
+      </c>
+      <c r="D104" t="n">
         <v>2520</v>
       </c>
-      <c r="D97" t="n">
-        <v>2460</v>
-      </c>
-      <c r="E97" t="n">
-        <v>2510</v>
-      </c>
-      <c r="F97" s="4" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="H97" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
+      <c r="E104" t="n">
+        <v>2570</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4467,7 +4761,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Scalping Signal List — 2026-05-13</t>
+          <t>Scalping — Review sesi market 2026-05-13</t>
         </is>
       </c>
     </row>

--- a/data/performance/daily/signal_list_2026-05-13.xlsx
+++ b/data/performance/daily/signal_list_2026-05-13.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-05-13.xlsx
+++ b/data/performance/daily/signal_list_2026-05-13.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-05-13.xlsx
+++ b/data/performance/daily/signal_list_2026-05-13.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -563,12 +569,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,17 +611,22 @@
       <c r="G6" s="4" t="n">
         <v>-2.63</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,12 +663,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -689,12 +710,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -731,12 +757,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -773,12 +804,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -815,12 +851,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -852,17 +893,22 @@
       <c r="G12" s="4" t="n">
         <v>-0.57</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -899,12 +945,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -936,17 +987,22 @@
       <c r="G14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -983,12 +1039,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1020,17 +1081,22 @@
       <c r="G16" s="4" t="n">
         <v>-0.42</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1067,12 +1133,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1109,12 +1180,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1151,12 +1227,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1193,12 +1274,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1235,12 +1321,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1277,12 +1368,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1314,17 +1410,22 @@
       <c r="G23" s="4" t="n">
         <v>-1.63</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1361,12 +1462,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1403,12 +1509,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1440,17 +1551,22 @@
       <c r="G26" s="4" t="n">
         <v>-1.34</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1487,12 +1603,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1529,12 +1650,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1566,17 +1692,22 @@
       <c r="G29" s="4" t="n">
         <v>-2.39</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1608,17 +1739,22 @@
       <c r="G30" s="4" t="n">
         <v>-1.21</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1655,12 +1791,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1697,12 +1838,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1734,17 +1880,22 @@
       <c r="G33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1776,17 +1927,22 @@
       <c r="G34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1818,17 +1974,22 @@
       <c r="G35" s="4" t="n">
         <v>-1.23</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1865,12 +2026,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1907,12 +2073,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1949,12 +2120,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1986,17 +2162,22 @@
       <c r="G39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2033,12 +2214,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2075,12 +2261,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2112,17 +2303,22 @@
       <c r="G42" s="4" t="n">
         <v>-0.4</v>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2159,12 +2355,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2196,17 +2397,22 @@
       <c r="G44" s="4" t="n">
         <v>-0.62</v>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2243,12 +2449,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2285,12 +2496,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2327,12 +2543,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2369,12 +2590,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2411,12 +2637,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2453,12 +2684,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2495,12 +2731,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2532,17 +2773,22 @@
       <c r="G52" s="4" t="n">
         <v>-1.14</v>
       </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2579,12 +2825,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2621,12 +2872,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2663,12 +2919,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2705,12 +2966,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2742,17 +3008,22 @@
       <c r="G57" s="4" t="n">
         <v>-3.33</v>
       </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2789,12 +3060,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2826,17 +3102,22 @@
       <c r="G59" s="4" t="n">
         <v>-1.18</v>
       </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2868,17 +3149,22 @@
       <c r="G60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2910,17 +3196,22 @@
       <c r="G61" s="4" t="n">
         <v>-2.16</v>
       </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2952,17 +3243,22 @@
       <c r="G62" s="4" t="n">
         <v>-7.3</v>
       </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2999,12 +3295,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3041,12 +3342,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3078,17 +3384,22 @@
       <c r="G65" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3125,12 +3436,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3167,12 +3483,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3209,12 +3530,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3251,12 +3577,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3293,12 +3624,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3330,17 +3666,22 @@
       <c r="G71" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3372,17 +3713,22 @@
       <c r="G72" s="4" t="n">
         <v>-2.63</v>
       </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3419,12 +3765,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3456,17 +3807,22 @@
       <c r="G74" s="4" t="n">
         <v>-1.45</v>
       </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3498,17 +3854,22 @@
       <c r="G75" s="4" t="n">
         <v>-0.63</v>
       </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3545,12 +3906,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3582,17 +3948,22 @@
       <c r="G77" s="4" t="n">
         <v>-2.06</v>
       </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3624,17 +3995,22 @@
       <c r="G78" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3666,17 +4042,22 @@
       <c r="G79" s="4" t="n">
         <v>-4.94</v>
       </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3713,12 +4094,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3755,12 +4141,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3792,17 +4183,22 @@
       <c r="G82" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3839,12 +4235,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3876,17 +4277,22 @@
       <c r="G84" s="4" t="n">
         <v>-4.76</v>
       </c>
-      <c r="H84" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3923,12 +4329,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3965,12 +4376,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4002,17 +4418,22 @@
       <c r="G87" s="4" t="n">
         <v>-1.01</v>
       </c>
-      <c r="H87" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4049,12 +4470,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4086,17 +4512,22 @@
       <c r="G89" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H89" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4133,12 +4564,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4175,12 +4611,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4217,12 +4658,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4254,17 +4700,22 @@
       <c r="G93" s="4" t="n">
         <v>-0.75</v>
       </c>
-      <c r="H93" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4296,17 +4747,22 @@
       <c r="G94" s="4" t="n">
         <v>-4.17</v>
       </c>
-      <c r="H94" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4338,17 +4794,22 @@
       <c r="G95" s="4" t="n">
         <v>-0.51</v>
       </c>
-      <c r="H95" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4380,17 +4841,22 @@
       <c r="G96" s="4" t="n">
         <v>-1.79</v>
       </c>
-      <c r="H96" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4422,17 +4888,22 @@
       <c r="G97" s="4" t="n">
         <v>-3.85</v>
       </c>
-      <c r="H97" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4469,12 +4940,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4511,12 +4987,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4548,17 +5029,22 @@
       <c r="G100" s="4" t="n">
         <v>-7.52</v>
       </c>
-      <c r="H100" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4595,12 +5081,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4637,12 +5128,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4674,17 +5170,22 @@
       <c r="G103" s="4" t="n">
         <v>-1.72</v>
       </c>
-      <c r="H103" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4721,12 +5222,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4743,7 +5249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4753,9 +5259,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4785,7 +5292,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -4810,15 +5317,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>

--- a/data/performance/daily/signal_list_2026-05-13.xlsx
+++ b/data/performance/daily/signal_list_2026-05-13.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>8075</v>
       </c>
       <c r="D5" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E5" t="n">
         <v>7600</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>7800</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>-3.41</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>-5.88</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>76</v>
       </c>
       <c r="D6" t="n">
+        <v>77</v>
+      </c>
+      <c r="E6" t="n">
         <v>74</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>79</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>3.95</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-2.63</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>4390</v>
       </c>
       <c r="D7" t="n">
+        <v>4310</v>
+      </c>
+      <c r="E7" t="n">
         <v>4400</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>4570</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>4.1</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>0.23</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>795</v>
       </c>
       <c r="D8" t="n">
+        <v>795</v>
+      </c>
+      <c r="E8" t="n">
         <v>785</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>795</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-1.26</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>590</v>
       </c>
       <c r="D9" t="n">
+        <v>590</v>
+      </c>
+      <c r="E9" t="n">
         <v>585</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>590</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-0.85</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>3290</v>
       </c>
       <c r="D10" t="n">
+        <v>3290</v>
+      </c>
+      <c r="E10" t="n">
         <v>3340</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>3370</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>2.43</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>1.52</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>4560</v>
       </c>
       <c r="D11" t="n">
+        <v>4510</v>
+      </c>
+      <c r="E11" t="n">
         <v>4470</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>4510</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>-1.1</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-1.97</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -882,33 +909,36 @@
         <v>350</v>
       </c>
       <c r="D12" t="n">
+        <v>350</v>
+      </c>
+      <c r="E12" t="n">
         <v>348</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>352</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-0.57</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -929,33 +959,36 @@
         <v>1620</v>
       </c>
       <c r="D13" t="n">
-        <v>1635</v>
+        <v>1610</v>
       </c>
       <c r="E13" t="n">
         <v>1635</v>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>0.93</v>
+      <c r="F13" t="n">
+        <v>1635</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H13" s="4" t="n">
+        <v>0.93</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -979,30 +1012,33 @@
         <v>152</v>
       </c>
       <c r="E14" t="n">
+        <v>152</v>
+      </c>
+      <c r="F14" t="n">
         <v>153</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>0.66</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1023,33 +1059,36 @@
         <v>4100</v>
       </c>
       <c r="D15" t="n">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="E15" t="n">
         <v>4200</v>
       </c>
-      <c r="F15" s="4" t="n">
-        <v>2.44</v>
+      <c r="F15" t="n">
+        <v>4200</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>2.44</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H15" s="4" t="n">
+        <v>2.44</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1073,30 +1112,33 @@
         <v>2380</v>
       </c>
       <c r="E16" t="n">
+        <v>2380</v>
+      </c>
+      <c r="F16" t="n">
         <v>2400</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>-0.42</v>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1117,33 +1159,36 @@
         <v>16625</v>
       </c>
       <c r="D17" t="n">
+        <v>16625</v>
+      </c>
+      <c r="E17" t="n">
         <v>17225</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>17450</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>4.96</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>3.61</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1164,33 +1209,36 @@
         <v>1205</v>
       </c>
       <c r="D18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E18" t="n">
         <v>1230</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>1265</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>4.98</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>2.07</v>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1211,33 +1259,36 @@
         <v>131</v>
       </c>
       <c r="D19" t="n">
+        <v>134</v>
+      </c>
+      <c r="E19" t="n">
         <v>138</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>140</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>6.87</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>5.34</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1258,33 +1309,36 @@
         <v>4500</v>
       </c>
       <c r="D20" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E20" t="n">
         <v>4490</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>4500</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>-0.22</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1305,33 +1359,36 @@
         <v>131</v>
       </c>
       <c r="D21" t="n">
+        <v>130</v>
+      </c>
+      <c r="E21" t="n">
         <v>151</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>153</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>16.79</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>15.27</v>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1352,33 +1409,36 @@
         <v>6075</v>
       </c>
       <c r="D22" t="n">
+        <v>6025</v>
+      </c>
+      <c r="E22" t="n">
         <v>5875</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>6050</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>-0.41</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>-3.29</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1399,33 +1459,36 @@
         <v>123</v>
       </c>
       <c r="D23" t="n">
+        <v>122</v>
+      </c>
+      <c r="E23" t="n">
         <v>121</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>124</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>-1.63</v>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1446,33 +1509,36 @@
         <v>336</v>
       </c>
       <c r="D24" t="n">
+        <v>336</v>
+      </c>
+      <c r="E24" t="n">
         <v>330</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>336</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>-1.79</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1493,33 +1559,36 @@
         <v>430</v>
       </c>
       <c r="D25" t="n">
+        <v>428</v>
+      </c>
+      <c r="E25" t="n">
         <v>410</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>430</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>-4.65</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1540,33 +1609,36 @@
         <v>1495</v>
       </c>
       <c r="D26" t="n">
+        <v>1495</v>
+      </c>
+      <c r="E26" t="n">
         <v>1475</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>1500</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>-1.34</v>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1587,33 +1659,36 @@
         <v>500</v>
       </c>
       <c r="D27" t="n">
+        <v>515</v>
+      </c>
+      <c r="E27" t="n">
         <v>510</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>515</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1634,33 +1709,36 @@
         <v>336</v>
       </c>
       <c r="D28" t="n">
+        <v>318</v>
+      </c>
+      <c r="E28" t="n">
         <v>320</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>322</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>-4.17</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>-4.76</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1681,33 +1759,36 @@
         <v>6275</v>
       </c>
       <c r="D29" t="n">
+        <v>6200</v>
+      </c>
+      <c r="E29" t="n">
         <v>6125</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>6300</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>-2.39</v>
       </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1728,33 +1809,36 @@
         <v>330</v>
       </c>
       <c r="D30" t="n">
+        <v>332</v>
+      </c>
+      <c r="E30" t="n">
         <v>326</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>344</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>4.24</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>-1.21</v>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1775,33 +1859,36 @@
         <v>114</v>
       </c>
       <c r="D31" t="n">
+        <v>112</v>
+      </c>
+      <c r="E31" t="n">
         <v>115</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>119</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>4.39</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1822,33 +1909,36 @@
         <v>1730</v>
       </c>
       <c r="D32" t="n">
+        <v>1730</v>
+      </c>
+      <c r="E32" t="n">
         <v>1735</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>1745</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>0.29</v>
       </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1872,30 +1962,33 @@
         <v>1020</v>
       </c>
       <c r="E33" t="n">
+        <v>1020</v>
+      </c>
+      <c r="F33" t="n">
         <v>1030</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1916,33 +2009,36 @@
         <v>266</v>
       </c>
       <c r="D34" t="n">
+        <v>264</v>
+      </c>
+      <c r="E34" t="n">
         <v>266</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>270</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="G34" s="4" t="n">
         <v>1.5</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1963,33 +2059,36 @@
         <v>324</v>
       </c>
       <c r="D35" t="n">
+        <v>314</v>
+      </c>
+      <c r="E35" t="n">
         <v>320</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>330</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>1.85</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>-1.23</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2010,33 +2109,36 @@
         <v>70</v>
       </c>
       <c r="D36" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E36" t="n">
         <v>74</v>
       </c>
-      <c r="F36" s="4" t="n">
-        <v>5.71</v>
+      <c r="F36" t="n">
+        <v>74</v>
       </c>
       <c r="G36" s="4" t="n">
         <v>5.71</v>
       </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H36" s="4" t="n">
+        <v>5.71</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2062,28 +2164,31 @@
       <c r="E37" t="n">
         <v>334</v>
       </c>
-      <c r="F37" s="4" t="n">
-        <v>0</v>
+      <c r="F37" t="n">
+        <v>334</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H37" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2104,33 +2209,36 @@
         <v>2460</v>
       </c>
       <c r="D38" t="n">
+        <v>2460</v>
+      </c>
+      <c r="E38" t="n">
         <v>2420</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>2460</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <v>-1.63</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2154,30 +2262,33 @@
         <v>1860</v>
       </c>
       <c r="E39" t="n">
+        <v>1860</v>
+      </c>
+      <c r="F39" t="n">
         <v>1865</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="G39" s="4" t="n">
         <v>0.27</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2198,33 +2309,36 @@
         <v>695</v>
       </c>
       <c r="D40" t="n">
+        <v>760</v>
+      </c>
+      <c r="E40" t="n">
         <v>715</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>760</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>9.35</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>2.88</v>
       </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2245,33 +2359,36 @@
         <v>3640</v>
       </c>
       <c r="D41" t="n">
+        <v>3590</v>
+      </c>
+      <c r="E41" t="n">
         <v>3670</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>3700</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>1.65</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2292,33 +2409,36 @@
         <v>1235</v>
       </c>
       <c r="D42" t="n">
+        <v>1240</v>
+      </c>
+      <c r="E42" t="n">
         <v>1230</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>1240</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="G42" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>-0.4</v>
       </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2339,33 +2459,36 @@
         <v>480</v>
       </c>
       <c r="D43" t="n">
+        <v>464</v>
+      </c>
+      <c r="E43" t="n">
         <v>472</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>478</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="G43" s="4" t="n">
         <v>-0.42</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="H43" s="4" t="n">
         <v>-1.67</v>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2386,33 +2509,36 @@
         <v>1615</v>
       </c>
       <c r="D44" t="n">
+        <v>1615</v>
+      </c>
+      <c r="E44" t="n">
         <v>1605</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>1620</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="G44" s="4" t="n">
         <v>0.31</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <v>-0.62</v>
       </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2433,33 +2559,36 @@
         <v>12900</v>
       </c>
       <c r="D45" t="n">
+        <v>13175</v>
+      </c>
+      <c r="E45" t="n">
         <v>13150</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>13500</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="G45" s="4" t="n">
         <v>4.65</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>1.94</v>
       </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2483,30 +2612,33 @@
         <v>560</v>
       </c>
       <c r="E46" t="n">
+        <v>560</v>
+      </c>
+      <c r="F46" t="n">
         <v>565</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="G46" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="H46" s="4" t="n">
         <v>-0.88</v>
       </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2527,33 +2659,36 @@
         <v>76</v>
       </c>
       <c r="D47" t="n">
+        <v>80</v>
+      </c>
+      <c r="E47" t="n">
         <v>82</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>83</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="G47" s="4" t="n">
         <v>9.210000000000001</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>7.89</v>
       </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2574,33 +2709,36 @@
         <v>378</v>
       </c>
       <c r="D48" t="n">
+        <v>372</v>
+      </c>
+      <c r="E48" t="n">
         <v>406</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>416</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="G48" s="4" t="n">
         <v>10.05</v>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="H48" s="4" t="n">
         <v>7.41</v>
       </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2621,33 +2759,36 @@
         <v>765</v>
       </c>
       <c r="D49" t="n">
+        <v>765</v>
+      </c>
+      <c r="E49" t="n">
         <v>770</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>775</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="G49" s="4" t="n">
         <v>1.31</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="H49" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2668,33 +2809,36 @@
         <v>2570</v>
       </c>
       <c r="D50" t="n">
+        <v>2570</v>
+      </c>
+      <c r="E50" t="n">
         <v>2550</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>2570</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="G50" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="H50" s="4" t="n">
         <v>-0.78</v>
       </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2715,33 +2859,36 @@
         <v>346</v>
       </c>
       <c r="D51" t="n">
+        <v>340</v>
+      </c>
+      <c r="E51" t="n">
         <v>356</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>374</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="G51" s="4" t="n">
         <v>8.09</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="H51" s="4" t="n">
         <v>2.89</v>
       </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2762,33 +2909,36 @@
         <v>875</v>
       </c>
       <c r="D52" t="n">
+        <v>890</v>
+      </c>
+      <c r="E52" t="n">
         <v>865</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>890</v>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="G52" s="4" t="n">
         <v>1.71</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="H52" s="4" t="n">
         <v>-1.14</v>
       </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2809,33 +2959,36 @@
         <v>7650</v>
       </c>
       <c r="D53" t="n">
+        <v>6600</v>
+      </c>
+      <c r="E53" t="n">
         <v>6875</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>7350</v>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="G53" s="4" t="n">
         <v>-3.92</v>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="H53" s="4" t="n">
         <v>-10.13</v>
       </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2861,28 +3014,31 @@
       <c r="E54" t="n">
         <v>555</v>
       </c>
-      <c r="F54" s="4" t="n">
-        <v>0.91</v>
+      <c r="F54" t="n">
+        <v>555</v>
       </c>
       <c r="G54" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="H54" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H54" s="4" t="n">
+        <v>0.91</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2903,33 +3059,36 @@
         <v>610</v>
       </c>
       <c r="D55" t="n">
-        <v>610</v>
+        <v>585</v>
       </c>
       <c r="E55" t="n">
         <v>610</v>
       </c>
-      <c r="F55" s="4" t="n">
-        <v>0</v>
+      <c r="F55" t="n">
+        <v>610</v>
       </c>
       <c r="G55" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H55" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2953,30 +3112,33 @@
         <v>125</v>
       </c>
       <c r="E56" t="n">
+        <v>125</v>
+      </c>
+      <c r="F56" t="n">
         <v>130</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="G56" s="4" t="n">
         <v>4.84</v>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="H56" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2997,33 +3159,36 @@
         <v>90</v>
       </c>
       <c r="D57" t="n">
+        <v>89</v>
+      </c>
+      <c r="E57" t="n">
         <v>87</v>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>93</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="G57" s="4" t="n">
         <v>3.33</v>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="H57" s="4" t="n">
         <v>-3.33</v>
       </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3044,33 +3209,36 @@
         <v>270</v>
       </c>
       <c r="D58" t="n">
+        <v>268</v>
+      </c>
+      <c r="E58" t="n">
         <v>274</v>
       </c>
-      <c r="E58" t="n">
+      <c r="F58" t="n">
         <v>284</v>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="G58" s="4" t="n">
         <v>5.19</v>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="H58" s="4" t="n">
         <v>1.48</v>
       </c>
-      <c r="H58" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3091,33 +3259,36 @@
         <v>8450</v>
       </c>
       <c r="D59" t="n">
+        <v>8425</v>
+      </c>
+      <c r="E59" t="n">
         <v>8350</v>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>8550</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="G59" s="4" t="n">
         <v>1.18</v>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="H59" s="4" t="n">
         <v>-1.18</v>
       </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3138,33 +3309,36 @@
         <v>60</v>
       </c>
       <c r="D60" t="n">
+        <v>59</v>
+      </c>
+      <c r="E60" t="n">
         <v>60</v>
       </c>
-      <c r="E60" t="n">
+      <c r="F60" t="n">
         <v>62</v>
       </c>
-      <c r="F60" s="4" t="n">
+      <c r="G60" s="4" t="n">
         <v>3.33</v>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="H60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3185,33 +3359,36 @@
         <v>139</v>
       </c>
       <c r="D61" t="n">
+        <v>135</v>
+      </c>
+      <c r="E61" t="n">
         <v>136</v>
       </c>
-      <c r="E61" t="n">
+      <c r="F61" t="n">
         <v>144</v>
       </c>
-      <c r="F61" s="4" t="n">
+      <c r="G61" s="4" t="n">
         <v>3.6</v>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="H61" s="4" t="n">
         <v>-2.16</v>
       </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3232,33 +3409,36 @@
         <v>178</v>
       </c>
       <c r="D62" t="n">
+        <v>175</v>
+      </c>
+      <c r="E62" t="n">
         <v>165</v>
       </c>
-      <c r="E62" t="n">
+      <c r="F62" t="n">
         <v>184</v>
       </c>
-      <c r="F62" s="4" t="n">
+      <c r="G62" s="4" t="n">
         <v>3.37</v>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="H62" s="4" t="n">
         <v>-7.3</v>
       </c>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3279,33 +3459,36 @@
         <v>800</v>
       </c>
       <c r="D63" t="n">
-        <v>880</v>
+        <v>810</v>
       </c>
       <c r="E63" t="n">
         <v>880</v>
       </c>
-      <c r="F63" s="4" t="n">
-        <v>10</v>
+      <c r="F63" t="n">
+        <v>880</v>
       </c>
       <c r="G63" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H63" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3326,33 +3509,36 @@
         <v>214</v>
       </c>
       <c r="D64" t="n">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="E64" t="n">
         <v>234</v>
       </c>
-      <c r="F64" s="4" t="n">
-        <v>9.35</v>
+      <c r="F64" t="n">
+        <v>234</v>
       </c>
       <c r="G64" s="4" t="n">
         <v>9.35</v>
       </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H64" s="4" t="n">
+        <v>9.35</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3373,33 +3559,36 @@
         <v>48</v>
       </c>
       <c r="D65" t="n">
+        <v>47</v>
+      </c>
+      <c r="E65" t="n">
         <v>48</v>
       </c>
-      <c r="E65" t="n">
+      <c r="F65" t="n">
         <v>49</v>
       </c>
-      <c r="F65" s="4" t="n">
+      <c r="G65" s="4" t="n">
         <v>2.08</v>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="H65" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3420,33 +3609,36 @@
         <v>110</v>
       </c>
       <c r="D66" t="n">
+        <v>108</v>
+      </c>
+      <c r="E66" t="n">
         <v>105</v>
       </c>
-      <c r="E66" t="n">
+      <c r="F66" t="n">
         <v>109</v>
       </c>
-      <c r="F66" s="4" t="n">
+      <c r="G66" s="4" t="n">
         <v>-0.91</v>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="H66" s="4" t="n">
         <v>-4.55</v>
       </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3467,33 +3659,36 @@
         <v>232</v>
       </c>
       <c r="D67" t="n">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="E67" t="n">
         <v>244</v>
       </c>
-      <c r="F67" s="4" t="n">
-        <v>5.17</v>
+      <c r="F67" t="n">
+        <v>244</v>
       </c>
       <c r="G67" s="4" t="n">
         <v>5.17</v>
       </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H67" s="4" t="n">
+        <v>5.17</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3514,33 +3709,36 @@
         <v>76</v>
       </c>
       <c r="D68" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E68" t="n">
         <v>76</v>
       </c>
-      <c r="F68" s="4" t="n">
-        <v>0</v>
+      <c r="F68" t="n">
+        <v>76</v>
       </c>
       <c r="G68" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H68" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3561,33 +3759,36 @@
         <v>4740</v>
       </c>
       <c r="D69" t="n">
+        <v>4650</v>
+      </c>
+      <c r="E69" t="n">
         <v>4700</v>
       </c>
-      <c r="E69" t="n">
+      <c r="F69" t="n">
         <v>4740</v>
       </c>
-      <c r="F69" s="4" t="n">
+      <c r="G69" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="H69" s="4" t="n">
         <v>-0.84</v>
       </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3608,33 +3809,36 @@
         <v>89</v>
       </c>
       <c r="D70" t="n">
+        <v>89</v>
+      </c>
+      <c r="E70" t="n">
         <v>93</v>
       </c>
-      <c r="E70" t="n">
+      <c r="F70" t="n">
         <v>96</v>
       </c>
-      <c r="F70" s="4" t="n">
+      <c r="G70" s="4" t="n">
         <v>7.87</v>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="H70" s="4" t="n">
         <v>4.49</v>
       </c>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3655,33 +3859,36 @@
         <v>580</v>
       </c>
       <c r="D71" t="n">
+        <v>595</v>
+      </c>
+      <c r="E71" t="n">
         <v>580</v>
       </c>
-      <c r="E71" t="n">
+      <c r="F71" t="n">
         <v>600</v>
       </c>
-      <c r="F71" s="4" t="n">
+      <c r="G71" s="4" t="n">
         <v>3.45</v>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="H71" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I71" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3702,33 +3909,36 @@
         <v>76</v>
       </c>
       <c r="D72" t="n">
+        <v>76</v>
+      </c>
+      <c r="E72" t="n">
         <v>74</v>
       </c>
-      <c r="E72" t="n">
+      <c r="F72" t="n">
         <v>78</v>
       </c>
-      <c r="F72" s="4" t="n">
+      <c r="G72" s="4" t="n">
         <v>2.63</v>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="H72" s="4" t="n">
         <v>-2.63</v>
       </c>
-      <c r="H72" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I72" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3749,33 +3959,36 @@
         <v>226</v>
       </c>
       <c r="D73" t="n">
+        <v>226</v>
+      </c>
+      <c r="E73" t="n">
         <v>232</v>
       </c>
-      <c r="E73" t="n">
+      <c r="F73" t="n">
         <v>234</v>
       </c>
-      <c r="F73" s="4" t="n">
+      <c r="G73" s="4" t="n">
         <v>3.54</v>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="H73" s="4" t="n">
         <v>2.65</v>
       </c>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3796,33 +4009,36 @@
         <v>276</v>
       </c>
       <c r="D74" t="n">
+        <v>280</v>
+      </c>
+      <c r="E74" t="n">
         <v>272</v>
       </c>
-      <c r="E74" t="n">
+      <c r="F74" t="n">
         <v>282</v>
       </c>
-      <c r="F74" s="4" t="n">
+      <c r="G74" s="4" t="n">
         <v>2.17</v>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="H74" s="4" t="n">
         <v>-1.45</v>
       </c>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I74" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3843,33 +4059,36 @@
         <v>4740</v>
       </c>
       <c r="D75" t="n">
+        <v>4750</v>
+      </c>
+      <c r="E75" t="n">
         <v>4710</v>
       </c>
-      <c r="E75" t="n">
+      <c r="F75" t="n">
         <v>4770</v>
       </c>
-      <c r="F75" s="4" t="n">
+      <c r="G75" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="H75" s="4" t="n">
         <v>-0.63</v>
       </c>
-      <c r="H75" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I75" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3895,28 +4114,31 @@
       <c r="E76" t="n">
         <v>41</v>
       </c>
-      <c r="F76" s="4" t="n">
-        <v>2.5</v>
+      <c r="F76" t="n">
+        <v>41</v>
       </c>
       <c r="G76" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H76" s="4" t="n">
+        <v>2.5</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3937,33 +4159,36 @@
         <v>97</v>
       </c>
       <c r="D77" t="n">
+        <v>97</v>
+      </c>
+      <c r="E77" t="n">
         <v>95</v>
       </c>
-      <c r="E77" t="n">
+      <c r="F77" t="n">
         <v>103</v>
       </c>
-      <c r="F77" s="4" t="n">
+      <c r="G77" s="4" t="n">
         <v>6.19</v>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="H77" s="4" t="n">
         <v>-2.06</v>
       </c>
-      <c r="H77" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I77" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3984,33 +4209,36 @@
         <v>74</v>
       </c>
       <c r="D78" t="n">
+        <v>73</v>
+      </c>
+      <c r="E78" t="n">
         <v>74</v>
       </c>
-      <c r="E78" t="n">
+      <c r="F78" t="n">
         <v>78</v>
       </c>
-      <c r="F78" s="4" t="n">
+      <c r="G78" s="4" t="n">
         <v>5.41</v>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="H78" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I78" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4031,33 +4259,36 @@
         <v>81</v>
       </c>
       <c r="D79" t="n">
+        <v>83</v>
+      </c>
+      <c r="E79" t="n">
         <v>77</v>
       </c>
-      <c r="E79" t="n">
+      <c r="F79" t="n">
         <v>90</v>
       </c>
-      <c r="F79" s="4" t="n">
+      <c r="G79" s="4" t="n">
         <v>11.11</v>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="H79" s="4" t="n">
         <v>-4.94</v>
       </c>
-      <c r="H79" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I79" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4078,33 +4309,36 @@
         <v>44</v>
       </c>
       <c r="D80" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E80" t="n">
         <v>48</v>
       </c>
-      <c r="F80" s="4" t="n">
-        <v>9.09</v>
+      <c r="F80" t="n">
+        <v>48</v>
       </c>
       <c r="G80" s="4" t="n">
         <v>9.09</v>
       </c>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H80" s="4" t="n">
+        <v>9.09</v>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4125,33 +4359,36 @@
         <v>80</v>
       </c>
       <c r="D81" t="n">
+        <v>77</v>
+      </c>
+      <c r="E81" t="n">
         <v>76</v>
       </c>
-      <c r="E81" t="n">
+      <c r="F81" t="n">
         <v>80</v>
       </c>
-      <c r="F81" s="4" t="n">
+      <c r="G81" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="H81" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4175,30 +4412,33 @@
         <v>70</v>
       </c>
       <c r="E82" t="n">
+        <v>70</v>
+      </c>
+      <c r="F82" t="n">
         <v>72</v>
       </c>
-      <c r="F82" s="4" t="n">
+      <c r="G82" s="4" t="n">
         <v>2.86</v>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="H82" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4219,33 +4459,36 @@
         <v>910</v>
       </c>
       <c r="D83" t="n">
+        <v>900</v>
+      </c>
+      <c r="E83" t="n">
         <v>970</v>
       </c>
-      <c r="E83" t="n">
+      <c r="F83" t="n">
         <v>980</v>
       </c>
-      <c r="F83" s="4" t="n">
+      <c r="G83" s="4" t="n">
         <v>7.69</v>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="H83" s="4" t="n">
         <v>6.59</v>
       </c>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4266,33 +4509,36 @@
         <v>84</v>
       </c>
       <c r="D84" t="n">
+        <v>85</v>
+      </c>
+      <c r="E84" t="n">
         <v>80</v>
       </c>
-      <c r="E84" t="n">
+      <c r="F84" t="n">
         <v>85</v>
       </c>
-      <c r="F84" s="4" t="n">
+      <c r="G84" s="4" t="n">
         <v>1.19</v>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="H84" s="4" t="n">
         <v>-4.76</v>
       </c>
-      <c r="H84" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I84" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4313,33 +4559,36 @@
         <v>191</v>
       </c>
       <c r="D85" t="n">
+        <v>191</v>
+      </c>
+      <c r="E85" t="n">
         <v>193</v>
       </c>
-      <c r="E85" t="n">
+      <c r="F85" t="n">
         <v>198</v>
       </c>
-      <c r="F85" s="4" t="n">
+      <c r="G85" s="4" t="n">
         <v>3.66</v>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="H85" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4360,33 +4609,36 @@
         <v>84</v>
       </c>
       <c r="D86" t="n">
+        <v>80</v>
+      </c>
+      <c r="E86" t="n">
         <v>81</v>
       </c>
-      <c r="E86" t="n">
+      <c r="F86" t="n">
         <v>84</v>
       </c>
-      <c r="F86" s="4" t="n">
+      <c r="G86" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="4" t="n">
+      <c r="H86" s="4" t="n">
         <v>-3.57</v>
       </c>
-      <c r="H86" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4407,33 +4659,36 @@
         <v>99</v>
       </c>
       <c r="D87" t="n">
+        <v>100</v>
+      </c>
+      <c r="E87" t="n">
         <v>98</v>
       </c>
-      <c r="E87" t="n">
+      <c r="F87" t="n">
         <v>101</v>
       </c>
-      <c r="F87" s="4" t="n">
+      <c r="G87" s="4" t="n">
         <v>2.02</v>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="H87" s="4" t="n">
         <v>-1.01</v>
       </c>
-      <c r="H87" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I87" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4454,33 +4709,36 @@
         <v>83</v>
       </c>
       <c r="D88" t="n">
+        <v>82</v>
+      </c>
+      <c r="E88" t="n">
         <v>79</v>
       </c>
-      <c r="E88" t="n">
+      <c r="F88" t="n">
         <v>83</v>
       </c>
-      <c r="F88" s="4" t="n">
+      <c r="G88" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="H88" s="4" t="n">
         <v>-4.82</v>
       </c>
-      <c r="H88" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4501,33 +4759,36 @@
         <v>67</v>
       </c>
       <c r="D89" t="n">
+        <v>68</v>
+      </c>
+      <c r="E89" t="n">
         <v>67</v>
       </c>
-      <c r="E89" t="n">
+      <c r="F89" t="n">
         <v>68</v>
       </c>
-      <c r="F89" s="4" t="n">
+      <c r="G89" s="4" t="n">
         <v>1.49</v>
       </c>
-      <c r="G89" s="4" t="n">
+      <c r="H89" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H89" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I89" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4548,33 +4809,36 @@
         <v>155</v>
       </c>
       <c r="D90" t="n">
+        <v>155</v>
+      </c>
+      <c r="E90" t="n">
         <v>160</v>
       </c>
-      <c r="E90" t="n">
+      <c r="F90" t="n">
         <v>166</v>
       </c>
-      <c r="F90" s="4" t="n">
+      <c r="G90" s="4" t="n">
         <v>7.1</v>
       </c>
-      <c r="G90" s="4" t="n">
+      <c r="H90" s="4" t="n">
         <v>3.23</v>
       </c>
-      <c r="H90" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4595,33 +4859,36 @@
         <v>500</v>
       </c>
       <c r="D91" t="n">
+        <v>505</v>
+      </c>
+      <c r="E91" t="n">
         <v>590</v>
       </c>
-      <c r="E91" t="n">
+      <c r="F91" t="n">
         <v>605</v>
       </c>
-      <c r="F91" s="4" t="n">
+      <c r="G91" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="G91" s="4" t="n">
+      <c r="H91" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="H91" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4642,33 +4909,36 @@
         <v>330</v>
       </c>
       <c r="D92" t="n">
+        <v>316</v>
+      </c>
+      <c r="E92" t="n">
         <v>370</v>
       </c>
-      <c r="E92" t="n">
+      <c r="F92" t="n">
         <v>372</v>
       </c>
-      <c r="F92" s="4" t="n">
+      <c r="G92" s="4" t="n">
         <v>12.73</v>
       </c>
-      <c r="G92" s="4" t="n">
+      <c r="H92" s="4" t="n">
         <v>12.12</v>
       </c>
-      <c r="H92" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4689,33 +4959,36 @@
         <v>134</v>
       </c>
       <c r="D93" t="n">
+        <v>135</v>
+      </c>
+      <c r="E93" t="n">
         <v>133</v>
       </c>
-      <c r="E93" t="n">
+      <c r="F93" t="n">
         <v>137</v>
       </c>
-      <c r="F93" s="4" t="n">
+      <c r="G93" s="4" t="n">
         <v>2.24</v>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="H93" s="4" t="n">
         <v>-0.75</v>
       </c>
-      <c r="H93" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I93" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4736,33 +5009,36 @@
         <v>120</v>
       </c>
       <c r="D94" t="n">
+        <v>120</v>
+      </c>
+      <c r="E94" t="n">
         <v>115</v>
       </c>
-      <c r="E94" t="n">
+      <c r="F94" t="n">
         <v>127</v>
       </c>
-      <c r="F94" s="4" t="n">
+      <c r="G94" s="4" t="n">
         <v>5.83</v>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="H94" s="4" t="n">
         <v>-4.17</v>
       </c>
-      <c r="H94" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I94" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4783,33 +5059,36 @@
         <v>985</v>
       </c>
       <c r="D95" t="n">
+        <v>990</v>
+      </c>
+      <c r="E95" t="n">
         <v>980</v>
       </c>
-      <c r="E95" t="n">
+      <c r="F95" t="n">
         <v>1035</v>
       </c>
-      <c r="F95" s="4" t="n">
+      <c r="G95" s="4" t="n">
         <v>5.08</v>
       </c>
-      <c r="G95" s="4" t="n">
+      <c r="H95" s="4" t="n">
         <v>-0.51</v>
       </c>
-      <c r="H95" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I95" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4830,33 +5109,36 @@
         <v>224</v>
       </c>
       <c r="D96" t="n">
+        <v>224</v>
+      </c>
+      <c r="E96" t="n">
         <v>220</v>
       </c>
-      <c r="E96" t="n">
+      <c r="F96" t="n">
         <v>226</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="G96" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="G96" s="4" t="n">
+      <c r="H96" s="4" t="n">
         <v>-1.79</v>
       </c>
-      <c r="H96" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I96" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4877,33 +5159,36 @@
         <v>78</v>
       </c>
       <c r="D97" t="n">
+        <v>78</v>
+      </c>
+      <c r="E97" t="n">
         <v>75</v>
       </c>
-      <c r="E97" t="n">
+      <c r="F97" t="n">
         <v>79</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="G97" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="H97" s="4" t="n">
         <v>-3.85</v>
       </c>
-      <c r="H97" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I97" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4924,33 +5209,36 @@
         <v>515</v>
       </c>
       <c r="D98" t="n">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="E98" t="n">
         <v>520</v>
       </c>
-      <c r="F98" s="4" t="n">
-        <v>0.97</v>
+      <c r="F98" t="n">
+        <v>520</v>
       </c>
       <c r="G98" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="H98" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H98" s="4" t="n">
+        <v>0.97</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J98" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4971,33 +5259,36 @@
         <v>179</v>
       </c>
       <c r="D99" t="n">
+        <v>179</v>
+      </c>
+      <c r="E99" t="n">
         <v>180</v>
       </c>
-      <c r="E99" t="n">
+      <c r="F99" t="n">
         <v>185</v>
       </c>
-      <c r="F99" s="4" t="n">
+      <c r="G99" s="4" t="n">
         <v>3.35</v>
       </c>
-      <c r="G99" s="4" t="n">
+      <c r="H99" s="4" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="H99" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5018,33 +5309,36 @@
         <v>452</v>
       </c>
       <c r="D100" t="n">
+        <v>452</v>
+      </c>
+      <c r="E100" t="n">
         <v>418</v>
       </c>
-      <c r="E100" t="n">
+      <c r="F100" t="n">
         <v>456</v>
       </c>
-      <c r="F100" s="4" t="n">
+      <c r="G100" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="G100" s="4" t="n">
+      <c r="H100" s="4" t="n">
         <v>-7.52</v>
       </c>
-      <c r="H100" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I100" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5065,33 +5359,36 @@
         <v>51</v>
       </c>
       <c r="D101" t="n">
+        <v>51</v>
+      </c>
+      <c r="E101" t="n">
         <v>52</v>
       </c>
-      <c r="E101" t="n">
+      <c r="F101" t="n">
         <v>53</v>
       </c>
-      <c r="F101" s="4" t="n">
+      <c r="G101" s="4" t="n">
         <v>3.92</v>
       </c>
-      <c r="G101" s="4" t="n">
+      <c r="H101" s="4" t="n">
         <v>1.96</v>
       </c>
-      <c r="H101" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5112,33 +5409,36 @@
         <v>585</v>
       </c>
       <c r="D102" t="n">
+        <v>575</v>
+      </c>
+      <c r="E102" t="n">
         <v>600</v>
       </c>
-      <c r="E102" t="n">
+      <c r="F102" t="n">
         <v>630</v>
       </c>
-      <c r="F102" s="4" t="n">
+      <c r="G102" s="4" t="n">
         <v>7.69</v>
       </c>
-      <c r="G102" s="4" t="n">
+      <c r="H102" s="4" t="n">
         <v>2.56</v>
       </c>
-      <c r="H102" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J102" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5159,33 +5459,36 @@
         <v>8725</v>
       </c>
       <c r="D103" t="n">
+        <v>8750</v>
+      </c>
+      <c r="E103" t="n">
         <v>8575</v>
       </c>
-      <c r="E103" t="n">
+      <c r="F103" t="n">
         <v>8750</v>
       </c>
-      <c r="F103" s="4" t="n">
+      <c r="G103" s="4" t="n">
         <v>0.29</v>
       </c>
-      <c r="G103" s="4" t="n">
+      <c r="H103" s="4" t="n">
         <v>-1.72</v>
       </c>
-      <c r="H103" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I103" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5206,33 +5509,36 @@
         <v>2600</v>
       </c>
       <c r="D104" t="n">
+        <v>2570</v>
+      </c>
+      <c r="E104" t="n">
         <v>2520</v>
       </c>
-      <c r="E104" t="n">
+      <c r="F104" t="n">
         <v>2570</v>
       </c>
-      <c r="F104" s="4" t="n">
+      <c r="G104" s="4" t="n">
         <v>-1.15</v>
       </c>
-      <c r="G104" s="4" t="n">
+      <c r="H104" s="4" t="n">
         <v>-3.08</v>
       </c>
-      <c r="H104" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+      <c r="J104" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5249,7 +5555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5257,12 +5563,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5292,45 +5599,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
